--- a/astro-site/public/dl/haccp-templates/BONUS-01-food-safety-training-log.xlsx
+++ b/astro-site/public/dl/haccp-templates/BONUS-01-food-safety-training-log.xlsx
@@ -1670,7 +1670,7 @@
     <row r="49" ht="24.5" customHeight="1">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>There is no single federal "food handler card": the Food Code requires the person in charge to be a Certified Food Protection Manager (§2-102.12), and many states and counties also require a food handler card for staff. The rules do not set a validity period for your own training, so the "Valid until" date is the renewal period set by the certificate or by your training plan; 2 to 5 years is typical. UK: no legal certificate; Level 2 is the usual standard.</t>
+          <t>There is no single federal "food handler card": under the Food Code, at least one supervisory employee must be a Certified Food Protection Manager (§2-102.12(A)), and many states and counties also require a food handler card for staff. The rules do not set a validity period for your own training, so the "Valid until" date is the renewal period set by the certificate or by your training plan; 2 to 5 years is typical. UK: no legal certificate; Level 2 is the usual standard.</t>
         </is>
       </c>
     </row>
